--- a/Shablon/WJ312A.xlsx
+++ b/Shablon/WJ312A.xlsx
@@ -5,7 +5,7 @@
   <workbookPr showInkAnnotation="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ITL\MEASControl\Shablon\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\my_doc\ITL\MEASControl\Shablon\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="134">
   <si>
     <t>3. Определение метрологических характеристик.</t>
   </si>
@@ -52,15 +52,6 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>АО "Гос МКБ "Вымпел" им. И.И. Торопова"</t>
-  </si>
-  <si>
-    <t>125424, г.Москва, Волоколамское шоссе, дом 90, стр. 23</t>
-  </si>
-  <si>
-    <t>Тел.+7 (495) 491-05-31, 22-68, e-mail: ogmetr@vympelmkb.com</t>
   </si>
   <si>
     <t>_type</t>
@@ -333,12 +324,6 @@
   </si>
   <si>
     <t>WJ-A-GS-E RevA 917106-00 Rev A МП</t>
-  </si>
-  <si>
-    <t>СГМетр, лаборатория средств электрических и радиотехнических измерений</t>
-  </si>
-  <si>
-    <t>Уникальный номер об аккредитации в реестре акредитованных лиц № РОСС СОБ 3.00231.2014</t>
   </si>
   <si>
     <t>Заключение:</t>
@@ -766,69 +751,69 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1148,74 +1133,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
+      <c r="A1" s="44"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
     </row>
     <row r="4" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
+      <c r="A4" s="45"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
     </row>
     <row r="5" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
+      <c r="A5" s="45"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
     </row>
     <row r="6" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1229,19 +1204,19 @@
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="48" t="str">
+      <c r="A7" s="28" t="str">
         <f>"Протокол поверки № 10/"&amp;C71&amp;"/"&amp;D10</f>
         <v>Протокол поверки № 10/_date/_numb</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
     </row>
     <row r="8" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="15"/>
@@ -1256,31 +1231,31 @@
       <c r="J8" s="15"/>
     </row>
     <row r="9" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
+      <c r="A9" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
       <c r="D9" s="19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E9" s="20"/>
       <c r="F9" s="21"/>
       <c r="G9" s="26" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H9" s="20"/>
       <c r="I9" s="20"/>
       <c r="J9" s="22"/>
     </row>
     <row r="10" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
+      <c r="A10" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="32"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="27" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E10" s="20"/>
       <c r="F10" s="20"/>
@@ -1290,11 +1265,11 @@
       <c r="J10" s="22"/>
     </row>
     <row r="11" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
+      <c r="A11" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="32"/>
+      <c r="C11" s="32"/>
       <c r="D11" s="19"/>
       <c r="E11" s="20"/>
       <c r="F11" s="20"/>
@@ -1304,11 +1279,11 @@
       <c r="J11" s="22"/>
     </row>
     <row r="12" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
+      <c r="A12" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
       <c r="D12" s="23"/>
       <c r="E12" s="20"/>
       <c r="F12" s="20"/>
@@ -1318,13 +1293,13 @@
       <c r="J12" s="22"/>
     </row>
     <row r="13" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
+      <c r="A13" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
       <c r="D13" s="27" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E13" s="20"/>
       <c r="F13" s="20"/>
@@ -1334,13 +1309,13 @@
       <c r="J13" s="22"/>
     </row>
     <row r="14" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="23" t="s">
         <v>83</v>
-      </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="23" t="s">
-        <v>86</v>
       </c>
       <c r="E14" s="20"/>
       <c r="F14" s="20"/>
@@ -1350,13 +1325,13 @@
       <c r="J14" s="22"/>
     </row>
     <row r="15" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
+      <c r="A15" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
       <c r="D15" s="19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E15" s="20"/>
       <c r="F15" s="20"/>
@@ -1379,7 +1354,7 @@
     </row>
     <row r="17" spans="1:10" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1391,112 +1366,112 @@
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="33"/>
+      <c r="G18" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="34"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="33"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37" t="s">
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="F18" s="37"/>
-      <c r="G18" s="36" t="s">
+      <c r="F20" s="30"/>
+      <c r="G20" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="31"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A21" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="36"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="37"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="44" t="s">
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="46" t="s">
+      <c r="F21" s="30"/>
+      <c r="G21" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="F20" s="46"/>
-      <c r="G20" s="47" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" s="47"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A21" s="44" t="s">
+      <c r="H21" s="31"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="44"/>
-      <c r="E21" s="46" t="s">
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="46"/>
-      <c r="G21" s="47" t="s">
+      <c r="F22" s="30"/>
+      <c r="G22" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="47"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="44" t="s">
+      <c r="H22" s="31"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A23" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="46" t="s">
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="46"/>
-      <c r="G22" s="47" t="s">
+      <c r="H23" s="31"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A24" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="H22" s="47"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="44" t="s">
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
-      <c r="D23" s="44"/>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="H23" s="47"/>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A24" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" s="47"/>
+      <c r="H24" s="31"/>
       <c r="I24" s="1"/>
     </row>
     <row r="25" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
@@ -1512,7 +1487,7 @@
     </row>
     <row r="26" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -1536,7 +1511,7 @@
     </row>
     <row r="28" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1560,7 +1535,7 @@
     </row>
     <row r="30" spans="1:10" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1597,621 +1572,621 @@
       <c r="J32" s="3"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="33"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
+      <c r="A33" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
     </row>
     <row r="34" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="J34" s="37"/>
+      <c r="A34" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="J34" s="33"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A35" s="36"/>
-      <c r="B35" s="37"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
+      <c r="A35" s="34"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" s="36"/>
-      <c r="B36" s="37"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="37"/>
-      <c r="I36" s="37"/>
-      <c r="J36" s="37"/>
+      <c r="A36" s="34"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="36"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="37"/>
+      <c r="A37" s="34"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="36"/>
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
       <c r="G38" s="13" t="s">
         <v>9</v>
       </c>
       <c r="H38" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="I38" s="37"/>
-      <c r="J38" s="37"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="37" t="s">
+      <c r="A39" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B39" s="45"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="45"/>
+      <c r="B39" s="40"/>
+      <c r="C39" s="40"/>
+      <c r="D39" s="40"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="40"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="40"/>
     </row>
     <row r="40" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C40" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34" t="s">
-        <v>92</v>
-      </c>
-      <c r="F40" s="34"/>
+        <v>42</v>
+      </c>
+      <c r="C40" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="F40" s="37"/>
       <c r="G40" s="12" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="I40" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="I40" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="J40" s="35"/>
+      <c r="J40" s="39"/>
     </row>
     <row r="41" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="F41" s="34"/>
+        <v>43</v>
+      </c>
+      <c r="C41" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="F41" s="37"/>
       <c r="G41" s="12" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="I41" s="35" t="s">
+        <v>101</v>
+      </c>
+      <c r="I41" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="J41" s="35"/>
+      <c r="J41" s="39"/>
     </row>
     <row r="42" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="F42" s="34"/>
+        <v>44</v>
+      </c>
+      <c r="C42" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="F42" s="37"/>
       <c r="G42" s="12" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="I42" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="I42" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="J42" s="35"/>
+      <c r="J42" s="39"/>
     </row>
     <row r="43" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C43" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="F43" s="34"/>
+        <v>45</v>
+      </c>
+      <c r="C43" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="F43" s="37"/>
       <c r="G43" s="12" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H43" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="I43" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="I43" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="J43" s="35"/>
+      <c r="J43" s="39"/>
     </row>
     <row r="44" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C44" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="F44" s="34"/>
+        <v>46</v>
+      </c>
+      <c r="C44" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="F44" s="37"/>
       <c r="G44" s="12" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="I44" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="I44" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="J44" s="35"/>
+      <c r="J44" s="39"/>
     </row>
     <row r="45" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="F45" s="34"/>
+        <v>47</v>
+      </c>
+      <c r="C45" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="F45" s="37"/>
       <c r="G45" s="12" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H45" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="I45" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="I45" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="35"/>
+      <c r="J45" s="39"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A46" s="38" t="s">
+      <c r="A46" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B46" s="39"/>
-      <c r="C46" s="39"/>
-      <c r="D46" s="39"/>
-      <c r="E46" s="39"/>
-      <c r="F46" s="39"/>
-      <c r="G46" s="39"/>
-      <c r="H46" s="39"/>
-      <c r="I46" s="39"/>
-      <c r="J46" s="39"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
     </row>
     <row r="47" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="C47" s="34" t="s">
-        <v>115</v>
-      </c>
-      <c r="D47" s="34"/>
-      <c r="E47" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="F47" s="34"/>
+        <v>42</v>
+      </c>
+      <c r="C47" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="D47" s="37"/>
+      <c r="E47" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="F47" s="37"/>
       <c r="G47" s="12" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="I47" s="35" t="s">
+        <v>113</v>
+      </c>
+      <c r="I47" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="35"/>
+      <c r="J47" s="39"/>
     </row>
     <row r="48" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="F48" s="34"/>
+        <v>43</v>
+      </c>
+      <c r="C48" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="F48" s="37"/>
       <c r="G48" s="12" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="I48" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="I48" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="J48" s="35"/>
+      <c r="J48" s="39"/>
     </row>
     <row r="49" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C49" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="D49" s="34"/>
-      <c r="E49" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="F49" s="34"/>
+        <v>44</v>
+      </c>
+      <c r="C49" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="F49" s="37"/>
       <c r="G49" s="12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="I49" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="I49" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="J49" s="35"/>
+      <c r="J49" s="39"/>
     </row>
     <row r="50" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C50" s="34" t="s">
-        <v>123</v>
-      </c>
-      <c r="D50" s="34"/>
-      <c r="E50" s="34" t="s">
-        <v>124</v>
-      </c>
-      <c r="F50" s="34"/>
+        <v>45</v>
+      </c>
+      <c r="C50" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="D50" s="37"/>
+      <c r="E50" s="37" t="s">
+        <v>119</v>
+      </c>
+      <c r="F50" s="37"/>
       <c r="G50" s="12" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="I50" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="I50" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="J50" s="35"/>
+      <c r="J50" s="39"/>
     </row>
     <row r="51" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C51" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="D51" s="34"/>
-      <c r="E51" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="F51" s="34"/>
+        <v>46</v>
+      </c>
+      <c r="C51" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F51" s="37"/>
       <c r="G51" s="12" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H51" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I51" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="I51" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="J51" s="35"/>
+      <c r="J51" s="39"/>
     </row>
     <row r="52" spans="1:10" ht="13.5" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="F52" s="37"/>
+      <c r="G52" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="I52" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="39"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A54" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="B54" s="48"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="48"/>
+      <c r="E54" s="48"/>
+      <c r="F54" s="48"/>
+      <c r="G54" s="48"/>
+      <c r="H54" s="48"/>
+      <c r="I54" s="48"/>
+      <c r="J54" s="48"/>
+    </row>
+    <row r="55" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C55" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="D55" s="33"/>
+      <c r="E55" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="F55" s="33"/>
+      <c r="G55" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="H55" s="33"/>
+      <c r="I55" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="C52" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="D52" s="34"/>
-      <c r="E52" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="F52" s="34"/>
-      <c r="G52" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="H52" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="I52" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="J52" s="35"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A54" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="33"/>
-      <c r="J54" s="33"/>
-    </row>
-    <row r="55" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="C55" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="F55" s="37"/>
-      <c r="G55" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="H55" s="37"/>
-      <c r="I55" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="J55" s="37"/>
+      <c r="J55" s="33"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A56" s="37"/>
-      <c r="B56" s="36"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="37"/>
-      <c r="I56" s="37"/>
-      <c r="J56" s="37"/>
+      <c r="A56" s="33"/>
+      <c r="B56" s="34"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="33"/>
+      <c r="E56" s="33"/>
+      <c r="F56" s="33"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="33"/>
+      <c r="I56" s="33"/>
+      <c r="J56" s="33"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A57" s="37"/>
-      <c r="B57" s="36"/>
-      <c r="C57" s="37"/>
-      <c r="D57" s="37"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="37"/>
-      <c r="G57" s="37"/>
-      <c r="H57" s="37"/>
-      <c r="I57" s="37"/>
-      <c r="J57" s="37"/>
+      <c r="A57" s="33"/>
+      <c r="B57" s="34"/>
+      <c r="C57" s="33"/>
+      <c r="D57" s="33"/>
+      <c r="E57" s="33"/>
+      <c r="F57" s="33"/>
+      <c r="G57" s="33"/>
+      <c r="H57" s="33"/>
+      <c r="I57" s="33"/>
+      <c r="J57" s="33"/>
     </row>
     <row r="58" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A58" s="14">
         <v>1</v>
       </c>
-      <c r="B58" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="C58" s="37">
+      <c r="B58" s="38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C58" s="33">
         <v>0.5</v>
       </c>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37">
+      <c r="D58" s="33"/>
+      <c r="E58" s="33">
         <v>500</v>
       </c>
-      <c r="F58" s="37"/>
-      <c r="G58" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="H58" s="42"/>
-      <c r="I58" s="37">
+      <c r="F58" s="33"/>
+      <c r="G58" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="H58" s="35"/>
+      <c r="I58" s="33">
         <v>3.5</v>
       </c>
-      <c r="J58" s="37"/>
+      <c r="J58" s="33"/>
     </row>
     <row r="59" spans="1:10" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A59" s="14">
         <v>2</v>
       </c>
-      <c r="B59" s="41"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="H59" s="42"/>
-      <c r="I59" s="37"/>
-      <c r="J59" s="37"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="33"/>
+      <c r="D59" s="33"/>
+      <c r="E59" s="33"/>
+      <c r="F59" s="33"/>
+      <c r="G59" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="H59" s="35"/>
+      <c r="I59" s="33"/>
+      <c r="J59" s="33"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A62" s="37" t="s">
+      <c r="A62" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="B62" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="B62" s="36" t="s">
+      <c r="C62" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="D62" s="38"/>
+      <c r="E62" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="C62" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="D62" s="41"/>
-      <c r="E62" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="F62" s="37"/>
-      <c r="G62" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="H62" s="37"/>
+      <c r="F62" s="33"/>
+      <c r="G62" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="H62" s="33"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A63" s="37"/>
-      <c r="B63" s="36"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="37"/>
-      <c r="H63" s="37"/>
+      <c r="A63" s="33"/>
+      <c r="B63" s="34"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="38"/>
+      <c r="E63" s="33"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A64" s="37"/>
-      <c r="B64" s="36"/>
-      <c r="C64" s="41"/>
-      <c r="D64" s="41"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="37"/>
+      <c r="A64" s="33"/>
+      <c r="B64" s="34"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="33"/>
+      <c r="F64" s="33"/>
+      <c r="G64" s="33"/>
+      <c r="H64" s="33"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A65" s="14">
         <v>1</v>
       </c>
-      <c r="B65" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="C65" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="D65" s="41"/>
-      <c r="E65" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="F65" s="42"/>
-      <c r="G65" s="37">
+      <c r="B65" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="C65" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="D65" s="38"/>
+      <c r="E65" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="F65" s="35"/>
+      <c r="G65" s="33">
         <v>100</v>
       </c>
-      <c r="H65" s="37"/>
+      <c r="H65" s="33"/>
     </row>
     <row r="66" spans="1:8" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A66" s="14">
         <v>2</v>
       </c>
-      <c r="B66" s="37"/>
-      <c r="C66" s="41"/>
-      <c r="D66" s="41"/>
-      <c r="E66" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="F66" s="42"/>
-      <c r="G66" s="37"/>
-      <c r="H66" s="37"/>
+      <c r="B66" s="33"/>
+      <c r="C66" s="38"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="F66" s="35"/>
+      <c r="G66" s="33"/>
+      <c r="H66" s="33"/>
     </row>
     <row r="69" spans="1:8" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A69" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="B69" s="30"/>
+      <c r="A69" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="B69" s="36"/>
       <c r="C69" s="24"/>
       <c r="D69" s="8"/>
       <c r="E69" s="10"/>
@@ -2220,32 +2195,32 @@
       <c r="H69" s="1"/>
     </row>
     <row r="70" spans="1:8" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A70" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="B70" s="30"/>
+      <c r="A70" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" s="36"/>
       <c r="C70" s="8"/>
       <c r="D70" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E70" s="46" t="s">
+        <v>55</v>
+      </c>
+      <c r="F70" s="47"/>
+      <c r="G70" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H70" s="11"/>
+    </row>
+    <row r="71" spans="1:8" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A71" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="E70" s="31" t="s">
+      <c r="B71" s="36"/>
+      <c r="C71" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="F70" s="32"/>
-      <c r="G70" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="H70" s="11"/>
-    </row>
-    <row r="71" spans="1:8" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A71" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="B71" s="30"/>
-      <c r="C71" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="D71" s="40"/>
+      <c r="D71" s="41"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -2253,6 +2228,86 @@
     </row>
   </sheetData>
   <mergeCells count="104">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="I52:J52"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A34:A38"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="C34:D38"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="E34:F38"/>
+    <mergeCell ref="I34:J38"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C62:D64"/>
+    <mergeCell ref="C65:D66"/>
+    <mergeCell ref="E62:F64"/>
+    <mergeCell ref="G62:H64"/>
+    <mergeCell ref="G65:H66"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="B62:B64"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="I55:J57"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="I58:J59"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="G59:H59"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="C55:D57"/>
+    <mergeCell ref="E55:F57"/>
+    <mergeCell ref="G55:H57"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C58:D59"/>
+    <mergeCell ref="E58:F59"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="I51:J51"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="G34:H37"/>
+    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="E24:F24"/>
@@ -2277,86 +2332,6 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="I55:J57"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="I58:J59"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="G59:H59"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="C55:D57"/>
-    <mergeCell ref="E55:F57"/>
-    <mergeCell ref="G55:H57"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:D59"/>
-    <mergeCell ref="E58:F59"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="I51:J51"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="G34:H37"/>
-    <mergeCell ref="A39:J39"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C62:D64"/>
-    <mergeCell ref="C65:D66"/>
-    <mergeCell ref="E62:F64"/>
-    <mergeCell ref="G62:H64"/>
-    <mergeCell ref="G65:H66"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="B62:B64"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="E34:F38"/>
-    <mergeCell ref="I34:J38"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="A46:J46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="I52:J52"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="C34:D38"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.39370078740157483" bottom="0.77083333333333337" header="0.51181102362204722" footer="0.51181102362204722"/>
